--- a/www/download/COUNTRY.ESP.EXI382.xlsx
+++ b/www/download/COUNTRY.ESP.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0658</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>19.208</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12.827</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>13.131</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>13.612</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>14.158</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>15.004</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15.848</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>16.497</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>17.869</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>18.483</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>19.693</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>20.445</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>21.093</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>20.468</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>19.105</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>18.722</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>18.417</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>17.627</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>16.869</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>17.661</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>17.922</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18.099</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>18.56</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18.527</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>18.957</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>16.011</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>9.586</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>9.863</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10.374</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10.925</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>11.775</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12.652</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.202</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>13.931</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14.615</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>15.134</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>16.122</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>16.809</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>17.394</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>16.861</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>15.881</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>15.592</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15.394</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>14.574</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>14.065</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>13.99</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>14.662</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>14.886</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15.046</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>15.451</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15.447</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>15.789</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>36500.716</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>25676.724</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>26071.86</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>27260.777</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>28482.155</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>31060.884</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>31882.031</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>33082.922</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>34624.508</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>35276.335</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>37108.969</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>39989.019</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>41381.202</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>42579.125</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>41105.018</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>37872.225</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>36982.035</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>36223.614</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>34334.308</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>33069.119</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>32721.579</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>34186.183</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>34648.866</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>35017.46</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>35808.752</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>35578.385</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36374.493</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>35102.265</t>
+          <t>98387013976.9695</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23968.008</t>
+          <t>52760953658.5498</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24266.114</t>
+          <t>51832277147.3972</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25277.577</t>
+          <t>54837517836.894</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>26479.914</t>
+          <t>59868535377.6962</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28985.396</t>
+          <t>66850886659.0885</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>29768.741</t>
+          <t>69073438713.5004</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30993.92</t>
+          <t>74290310138.6659</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>32457.008</t>
+          <t>73406020076.9753</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>33253.823</t>
+          <t>83444102750.6387</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>34980.467</t>
+          <t>90274924818.5381</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>38186.063</t>
+          <t>95815445998.2311</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>40378.747</t>
+          <t>91652977283.1768</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>41522.652</t>
+          <t>93876257464.4987</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>40078.343</t>
+          <t>76777009940.7187</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>36714.646</t>
+          <t>71247544638.83</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>35886.87</t>
+          <t>72355191298.7256</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>35142.813</t>
+          <t>68651839883.8928</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>32348.009</t>
+          <t>68217065714.4966</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>31976.794</t>
+          <t>59032269340.7775</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>31623.479</t>
+          <t>56548842766.2902</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>33021.182</t>
+          <t>59621349030.2047</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>33435.679</t>
+          <t>61033423632.0788</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>33759.379</t>
+          <t>61859664774.5699</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>34507.019</t>
+          <t>64696428755.9992</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>34303.23</t>
+          <t>67921587930.6328</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>35044.413</t>
+          <t>67694202344.8762</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>40552011884.0923</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>14249897135.2749</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>14320917773.9035</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15682759182.4646</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>17020166003.8328</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>18178755848.7139</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19496204471.1624</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>20511058260.0363</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>18830282570.9857</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>20961125395.9382</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>22386768936.8628</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>22786158208.5214</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>21758303098.7674</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>24238384480.9071</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>19675451602.0103</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>18575127788.7111</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>18377704575.5618</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>18313009053.5919</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>17778220977.3555</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>16199786484.8815</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>15603697815.7647</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>17022675765.5568</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>19197248427.7687</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>24390922056.723</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>21598153544.6212</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>23244530130.5291</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>24688544924.9613</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>41505065.1221009</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10450800.6203225</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10337443.1495027</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10226013.2203518</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10067475.9373272</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10056710.6299108</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8944597.99258576</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9524293.64738611</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8066426.80477837</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>8714056.28429341</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>8277606.74205352</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>8242377.60327241</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6904686.63317012</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7724611.03983004</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7668255.19885205</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>7225538.7464851</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7012198.81801245</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7013308.52784933</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6725402.48021385</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>6556739.92278918</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>5636993.19846179</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5822955.16490417</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>6357920.13198619</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5816847.83485866</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>5587866.72845368</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>5516744.98374091</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>6218520.95439544</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>62668.7713721669</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>109150.259604509</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>119065.979339672</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>128313.113230816</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>141599.335596736</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>182802.150837199</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>186206.721577246</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>188266.093372559</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>179176.589949946</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>177778.402371401</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>197929.288950598</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>228149.77606841</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>241980.035572126</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>247036.974152177</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>234207.58335972</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>239905.363790184</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>240566.98723405</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>256048.55906578</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>234748.24278025</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>232479.317147626</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>258111.09646497</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>246989.914708342</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>261925.054227737</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>259687.480908882</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>286609.124111795</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>269685.138902615</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>266647.93492814</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>366747.69319344</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>400934.308307537</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>428996.269989853</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>466609.205005635</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>537337.757042776</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>717230.693236189</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>744110.989270828</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>775786.719826279</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>704167.915145618</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>782240.214946117</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>907242.39157551</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1030045.73782176</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1020822.80920255</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1050617.02993038</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>861065.614102239</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>921470.125118886</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>974212.781415882</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1020258.95994566</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>990305.727393516</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>887032.978261422</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>959868.377649722</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>922427.991310053</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>998329.242964741</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>984091.674582243</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1096596.10451857</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1095198.72526949</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1071643.91220365</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.134389052188936</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.681977615169554</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.694452435458917</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.611806743055159</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.555796458979479</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.594465333118474</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.526899302068776</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.511083416909023</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.723660166948995</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.586452176200736</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.562550946885391</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.675844723386752</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.855785665670259</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.713094865406691</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.03697194914237</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.97654875949421</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.952739519369092</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.919008115878249</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.819530172746379</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.973902168018022</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.0266656899055</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.939835012797519</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.741691234229747</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.384096052904784</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.597683746365345</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.475754934274652</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.419460439164896</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2532.7476412552</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1486.57866773179</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1451.96923623444</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1511.67866888323</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1557.96697397006</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1543.80405159166</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1540.94612524121</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1553.6444193661</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1351.6432354957</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1434.21019328864</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1479.23674751342</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1413.37556653222</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1294.41283441204</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1393.49111652942</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1166.92079959755</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1169.65944969484</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1178.66998733705</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1189.62764819803</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1219.90057140394</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1151.81737934654</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1115.36440410999</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1161.00925646414</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1289.65467847727</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1621.10258246219</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1397.83025384929</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1504.77952283454</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1563.65013149628</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>55014459294.1979</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>14856363248.1533</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>14664358326.3896</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>14336606853.5717</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>14568429273.5909</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>14644096969.8684</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>16525143141.9482</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>17450395562.3358</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>16528633989.4554</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>17461169285.1483</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>17823105136.5644</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>15140187575.4434</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>15211851480.5018</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>16244956407.4931</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>17109033126.9508</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>18013883582.2093</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>19617627392.642</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>20749886108.2898</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>22542793413.9904</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>19599179603.0986</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>18666381940.7546</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>22200359308.425</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>23310752972.2871</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>26926472463.6202</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>23948925674.5122</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>27606594969.0218</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>28002090790.7624</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>51900116992.9368</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10955952909.3258</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10565555691.6971</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>9891172438.08033</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>9926124429.60887</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10750181111.5569</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11893414758.1154</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12958287953.0195</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>12030058231.4512</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>14347204117.234</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>12895758055.9333</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>12137673690.3249</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>12815777658.3423</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>13034142844.4119</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>12986696908.0456</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>14137175730.729</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>15218485342.1267</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>16181268396.4334</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>17867303293.7008</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>15206311235.798</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>14392603878.696</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>17296111966.6558</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>19615190017.7619</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>23264134881.42</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>20466508114.8436</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>23720152291.842</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>22848174488.9559</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3114342301.26114</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3900410338.82746</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4098802634.6925</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4445434415.49138</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4642304843.98203</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3893915858.31152</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4631728383.83279</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>4492107609.31627</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>4498575758.0042</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3113965167.91422</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4927347080.63111</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3002513885.11851</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2396073822.15945</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3210813563.08117</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4122336218.90523</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>3876707851.48035</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4399142050.51528</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>4568617711.85645</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>4675490120.28958</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>4392868367.30066</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>4273778062.05862</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>4904247341.76921</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>3695562954.52524</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>3662337582.20021</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>3482417559.66858</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3886442677.17982</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5153916301.80653</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>2192.37408631315</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>2500.39204231344</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>2460.29280854888</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>2436.53387183864</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>2423.87950130959</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2461.54204139074</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>2352.86956315639</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>2347.68631787736</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>2329.77360495</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.682</t>
+          <t>2275.30588227205</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>2311.38278049476</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>2368.59798533679</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.166</t>
+          <t>2402.15278356148</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2387.18247671638</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2376.98493565101</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.985</t>
+          <t>2311.88893432501</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>2301.63546456732</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.924</t>
+          <t>2282.90511176518</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.899</t>
+          <t>2219.64589742001</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.927</t>
+          <t>2273.57482225298</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>2260.4707695516</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2.086</t>
+          <t>2252.16640587116</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2.164</t>
+          <t>2246.18024868725</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.275</t>
+          <t>2243.76168573966</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.319</t>
+          <t>2233.29067675276</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>2220.68580581853</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2219.53950235396</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1900.24809645376</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>2001.72475891288</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>1985.45928080791</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>2002.76066002556</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>2011.72155868424</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>2070.11836527888</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>2011.78922991569</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>2005.39019215536</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>2013.04108697041</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>1974.15286723994</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2007.69171256407</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>2030.67254030739</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>2024.00573239682</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>2018.64726993455</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>2008.28710602613</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>1982.34082534281</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>1975.3355695729</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>1966.84678912538</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>1947.78061427104</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>1946.36688877562</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>1939.74974836827</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>1935.66868398201</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>1933.26603851705</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>1934.7518620582</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>1929.30134312979</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>1920.34139736842</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>1918.79103810903</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>79740.5875152095</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>133075.027819</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>155035.562841143</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>166547.867781614</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>181167.618576981</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>216936.915603916</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>230681.518227291</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>232505.711548607</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>234889.260452329</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>244093.383503889</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>259018.540946843</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>278068.885364289</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>303315.864256851</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>308888.717909339</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>278006.077584788</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>316068.443132119</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>358327.67375229</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>379057.759565008</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>392974.214169014</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>400533.454281016</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>424858.194002948</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>442881.323289154</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>481841.86211679</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>497226.994830444</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>511727.049226218</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>530470.325125534</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>546907.66608827</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8993633744.95429</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7750231215.07924</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8297168186.61468</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8882918427.05406</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>9581444937.02365</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>11232537570.5477</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11393056017.396</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11314300106.7824</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10838090712.8254</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>12547599276.9184</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>13039449382.8185</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12933602758.0459</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>12418417289.7324</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>13816845185.3874</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>11309399513.8216</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>11950058052.3856</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>13881680078.8843</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14002550434.7491</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>15301123348.8048</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>13614931560.4147</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>12525142113.5191</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>13942679238.8746</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>16565544024.2154</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16595808831.44</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>17645528891.3172</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18728915561.72</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>18099785360.7773</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>86631.4704844632</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>134269.948990381</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>153855.860580955</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>169853.543543822</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>196227.305155915</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>241920.634636083</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>251513.498557118</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>251935.342954878</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>257984.237378779</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>285614.62216522</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>317263.695380431</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>352771.601707063</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>384494.159462588</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>377334.534336997</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>290146.313220166</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>330434.759033937</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>354482.084640175</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>351203.860130928</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>340553.300848323</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>358743.552607855</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>382020.923125488</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>384825.776983961</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>427036.267287585</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>454362.869940396</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>462729.176919142</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>477571.479849964</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>489964.443176601</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>36500.716</t>
+          <t>67911959055.9252</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25676.724</t>
+          <t>22849328418.4768</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26071.86</t>
+          <t>22740700739.9598</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27260.777</t>
+          <t>23842309042.4309</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28482.155</t>
+          <t>26912481741.8495</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>31060.884</t>
+          <t>29752623161.1744</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>31882.031</t>
+          <t>31277959876.6017</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>33082.922</t>
+          <t>32015924882.0554</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>34624.508</t>
+          <t>31290045273.1745</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>35276.335</t>
+          <t>37623341945.2667</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>37108.969</t>
+          <t>40604090632.0181</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>39989.019</t>
+          <t>39188934462.4265</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>41381.202</t>
+          <t>37711184622.9696</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>42579.125</t>
+          <t>39441571748.5062</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>41105.018</t>
+          <t>30205371041.4861</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>37872.225</t>
+          <t>31735337353.3093</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>36982.035</t>
+          <t>33055850458.4624</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>36223.614</t>
+          <t>31715491584.412</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>34334.308</t>
+          <t>31838914690.7825</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>33069.119</t>
+          <t>28771590008.9437</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>32721.579</t>
+          <t>27050664259.6348</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>34186.183</t>
+          <t>29985868657.8408</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>34648.866</t>
+          <t>34597271002.2645</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>35017.46</t>
+          <t>39262028517.6514</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>35808.752</t>
+          <t>37122545856.0623</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>35578.385</t>
+          <t>41202136418.7352</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>36374.493</t>
+          <t>40553609014.1444</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>35102.265</t>
+          <t>-6890.88296925372</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23968.008</t>
+          <t>-1194.92117138057</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24266.114</t>
+          <t>1179.70226018777</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25277.577</t>
+          <t>-3305.67576220785</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>26479.914</t>
+          <t>-15059.6865789339</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28985.396</t>
+          <t>-24983.7190321673</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29768.741</t>
+          <t>-20831.980329827</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30993.92</t>
+          <t>-19429.6314062705</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>32457.008</t>
+          <t>-23094.97692645</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>33253.823</t>
+          <t>-41521.2386613306</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>34980.467</t>
+          <t>-58245.1544335884</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>38186.063</t>
+          <t>-74702.7163427745</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>40378.747</t>
+          <t>-81178.2952057367</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>41522.652</t>
+          <t>-68445.8164276584</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>40078.343</t>
+          <t>-12140.2356353782</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>36714.646</t>
+          <t>-14366.3159018176</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>35886.87</t>
+          <t>3845.58911211534</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>35142.813</t>
+          <t>27853.8994340799</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>32348.009</t>
+          <t>52420.9133206909</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>31976.794</t>
+          <t>41789.9016731618</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>31623.479</t>
+          <t>42837.2708774605</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>33021.182</t>
+          <t>58055.5463051936</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>33435.679</t>
+          <t>54805.5948292056</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>33759.379</t>
+          <t>42864.1248900485</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>34507.019</t>
+          <t>48997.8723070765</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>34303.23</t>
+          <t>52898.8452755702</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>35044.413</t>
+          <t>56943.2229116688</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>61369.004</t>
+          <t>-58918325310.9709</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>34954.828</t>
+          <t>-15099097203.3975</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34568.076</t>
+          <t>-14443532553.3451</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>36389.682</t>
+          <t>-14959390615.3768</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>39411.299</t>
+          <t>-17331036804.8259</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>43380.17</t>
+          <t>-18520085590.6266</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>44818.308</t>
+          <t>-19884903859.2057</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>47672.94</t>
+          <t>-20701624775.273</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>47448.736</t>
+          <t>-20451954560.3491</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>53161.741</t>
+          <t>-25075742668.3483</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>56996.271</t>
+          <t>-27564641249.1996</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>60155.553</t>
+          <t>-26255331704.3806</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>58710.378</t>
+          <t>-25292767333.2372</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>59961</t>
+          <t>-25624726563.1189</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>50318.648</t>
+          <t>-18895971527.6645</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>46380.087</t>
+          <t>-19785279300.9237</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>46794.872</t>
+          <t>-19174170379.5781</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>44510.99</t>
+          <t>-17712941149.6629</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>43868.302</t>
+          <t>-16537791341.9777</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>38539.154</t>
+          <t>-15156658448.529</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>36954.542</t>
+          <t>-14525522146.1157</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>39020.237</t>
+          <t>-16043189418.9662</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>40521.738</t>
+          <t>-18031726978.0491</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>41140.72</t>
+          <t>-22666219686.2114</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>42878.361</t>
+          <t>-19477016964.7452</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>44720.525</t>
+          <t>-22473220857.0152</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>44342.436</t>
+          <t>-22453823653.3671</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>160898.568031269</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>176212.853145676</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>175512.101889217</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>203471.995447856</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>221604.066873825</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>219068.983502845</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>244078.178542071</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>262473.597718302</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>268670.41270082</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>286751.366679587</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>320896.248406243</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>348758.596328187</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>354704.044822793</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>348721.974497402</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>332533.082723081</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>338259.634192764</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>324218.361106523</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>313066.162842927</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>309864.189805332</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>310910.038098964</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>334270.60459403</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>342145.072892162</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>347984.677259167</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>376669.770265065</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>382727.28137333</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>390594.704466612</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>405046.03705747</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>16812.085</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>14363.629</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>14385.815</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>15079.798</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>15776.566</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>17038.431</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>17284.973</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>18028.597</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>18678.273</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>18964.199</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>19694.904</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>21222.623</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>21725.799</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>22073.606</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>20883.145</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>18549.346</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>17867.011</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>17229.16</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>16170.598</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>15471.557</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>15206.13</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>15964.251</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>16012.937</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16323.866</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>16909.222</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16725.223</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>16843.766</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>240663.258797474</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>261756.458419507</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>267955.189121265</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>296178.976068549</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>320649.318823336</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>355823.401375211</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>386153.007151631</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>413342.439562233</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>427259.067940935</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>454145.270202545</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>490490.30775944</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>527183.167745986</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>553828.28452303</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>614802.597933762</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>576998.493924958</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>577083.916268271</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>571058.698602303</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>552269.571799132</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>550087.084238168</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>551305.225284563</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>581265.106824652</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>598667.502317449</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>633956.361979667</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>669847.628394944</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>665104.34798183</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>680895.568105966</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>763560.966914084</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>36246.816</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>12659.855</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>12910.936</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>14082.993</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>15182.606</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>16218.612</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17411.675</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>18350.658</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>17076.078</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>18933.713</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>20274.964</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>20511.998</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>19952.021</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>22119.539</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>18007.504</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>17015.013</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>16691.301</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>16644.391</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>16060.289</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>15067.852</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>14559.804</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>16051.994</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>18485.044</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>23477.017</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>20875.061</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>22424.474</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>23578.046</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>89.32</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>79.49</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>74.41</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>78.72</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>70.97</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>68.9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>90.07</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>75.63</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>72.53</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>86.16</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>102.38</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>87.72</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>122.56</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>115.78</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>111.14</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>101.42</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>112.22</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>117.2</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>105.71</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>80.88</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>52.97</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>48.63</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>38.743</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>9.108</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>9.109</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>8.926</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8.711</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>8.647</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7.632</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>8.159</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6.975</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>7.407</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>6.964</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>6.927</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>5.889</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6.521</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>6.612</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>6.103</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>5.888</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>5.612</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>5.547</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>4.801</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>5.004</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>5.677</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>5.028</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>4.849</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>4.736</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>5.348</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>240295.884102904</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>255250.611298707</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>264333.345942721</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>267606.468593984</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>286662.576277425</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>304988.367336907</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>328982.354924679</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>349168.641848709</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>386305.473328207</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>416750.382859778</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>447244.942021451</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>488068.368302311</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>537166.093167515</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>514276.749594085</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>521867.182270199</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>524052.590535417</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>520845.710344258</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>504991.001669298</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>498573.436287918</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>505370.838611444</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>520683.797673351</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>539228.506555739</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>549840.973503385</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>566322.781872015</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>607816.58918039</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>615760.041814406</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>536674.670901598</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>35102265442.6347</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>23968008000.0011</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>24266113999.9976</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>25277577000.0066</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>26479914000.006</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>28985395999.999</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>29768741000.0081</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>30993919999.9957</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>32457008000.002</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>33253823000.0027</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>34980466999.9994</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>38186063000.0063</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>40378747000.0014</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>41522651999.9951</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>40078343000.0034</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>36714645788.2233</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>35886869999.9896</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>35142812999.9948</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>32348009486.0509</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>31976793663.9366</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>31623478998.8638</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>33021182461.5269</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>33435679307.9756</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>33759378945.4186</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>34507018869.7443</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>34303230035.0241</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>35044412821.5279</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>36500716125.1982</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>25676724000.0017</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>26071859999.9982</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>27260777000.0063</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>28482155000.0059</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>31060883999.9999</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>31882031000.0083</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>33082921999.9957</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>34624508000.0016</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>35276335000.0029</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>37108968999.9996</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>39989019000.0058</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>41381202000.0017</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>42579124999.9951</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>41105018000.0037</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>37872225000.0054</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>36982034999.9897</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>36223613999.9945</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>34334308000.0037</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>33069118938.7597</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>32721578935.3163</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>34186182805.8568</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>34648866367.8214</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>35017459879.3931</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>35808751644.3015</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>35578385268.5515</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>36374492609.8103</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16812084709.312</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>14363629326.5151</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>14385814683.438</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>15079798169.4709</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>15776566454.7497</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>17038431263.3298</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>17284973285.3851</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>18028597432.5191</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>18678272719.1849</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>18964199220.2426</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>19694903859.5655</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>21222623176.5389</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>21725798545.3908</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>22073606202.916</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>20883144862.9487</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>18549345930.8088</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>17867010896.9215</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>17229159820.7789</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>16170598494.1149</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>15471557430.6123</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>15206130496.7365</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>15964250923.1019</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>16012936520.8841</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16323865885.7625</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>16909221820.6071</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16725222969.0567</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>16843765971.4328</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>19208395.0476339</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>12827299.9999993</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13131399.9999986</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>13611600.0000012</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>14158099.9999993</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15004400.0000046</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15847599.9999982</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>16497000.0000043</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>17200100.000001</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>17869100.0000029</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>18483399.9999964</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>19692500.0000012</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20445200.0000011</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>21092899.9999964</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>20467699.9999963</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>19104799.999998</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>18721900.0000014</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>18417099.9999967</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>17627400.0000012</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>16990177.5094222</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>16868969.2899003</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>17661174.7086437</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>17922451.2702864</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18099199.4715752</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>18560476.1909361</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18527114.666854</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>18956984.8343973</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16011074.780429</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>9585699.99999884</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>9863099.99999967</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10374400.0000016</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10924599.9999997</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>11775300.0000043</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12652099.9999988</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>13201900.0000045</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>13931400.0000007</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14615100.0000038</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>15133999.9999965</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>16121800.0000015</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>16809400.0000013</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>17393999.999996</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16860999.9999965</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>15880799.9999977</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>15591900.000001</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>15393899.9999969</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>14573500.0000002</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>14064544.2371013</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>13989775.6807254</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>14661963.8653006</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>14885572.6638664</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15045884.400281</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>15451199.0888343</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15447133.4689241</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>15789046.6848466</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>36500716125.1982</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>25676724000.0017</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>26071859999.9982</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>27260777000.0063</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>28482155000.0059</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>31060883999.9999</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>31882031000.0083</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>33082921999.9957</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>34624508000.0016</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>35276335000.0029</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>37108968999.9996</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>39989019000.0058</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>41381202000.0017</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>42579124999.9951</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>41105018000.0037</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>37872225000.0054</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>36982034999.9897</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>36223613999.9945</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>34334308000.0037</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>33069118938.7597</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>32721578935.3163</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>34186182805.8568</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>34648866367.8214</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>35017459879.3931</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>35808751644.3015</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>35578385268.5515</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>36374492609.8103</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>35102265442.6347</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>23968008000.0011</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24266113999.9976</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>25277577000.0066</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>26479914000.006</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>28985395999.999</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29768741000.0081</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>30993919999.9957</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>32457008000.002</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>33253823000.0027</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>34980466999.9994</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>38186063000.0063</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>40378747000.0014</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>41522651999.9951</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>40078343000.0034</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>36714645788.2233</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>35886869999.9896</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>35142812999.9948</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>32348009486.0509</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>31976793663.9366</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>31623478998.8638</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>33021182461.5269</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>33435679307.9756</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>33759378945.4186</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>34507018869.7443</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>34303230035.0241</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>35044412821.5279</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>859503.380100947</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>947116.541728794</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>982434.809862531</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1051129.48989046</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1147938.92242739</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1311295.89869531</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1431634.69507259</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1539707.90321317</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1657721.58924507</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1792743.78287627</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1980504.22952974</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2187462.84938103</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2308486.54247903</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2298966.76437042</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2099586.02604678</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2116019.76702789</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2103230.64554607</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2051045.42096355</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2023845.42637262</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2053554.69510555</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2157887.80565579</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2223132.542064</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2306474.18861627</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2424251.67725151</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2471195.08591979</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>2559136.06302147</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2555524.82365583</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>260509.777612203</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>284179.985901746</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>290278.957029927</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>321075.104292366</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>348012.140021471</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>383785.679510459</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>417507.472885858</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>445928.079913591</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>466802.96455133</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>497597.667025685</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>540731.334506873</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>580854.811044142</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>607610.867270418</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>663469.240934069</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>613234.278291308</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>618140.623543395</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>611392.85004188</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>594007.483071682</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>588619.148847485</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>593240.594263298</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>627363.176581258</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>647099.634472076</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>688456.241731773</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>717107.838366861</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>718831.200932094</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>735390.932981204</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>837472.893485185</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
